--- a/originales/respuestas/2025/01. Calificadas/bucle p28/Alcaldía Local De Chapinero.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p28/Alcaldía Local De Chapinero.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -258,6 +258,9 @@
     </xf>
     <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -473,10 +476,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="3" width="10.71"/>
-    <col customWidth="1" min="4" max="4" width="42.57"/>
-    <col customWidth="1" min="5" max="5" width="10.71"/>
-    <col customWidth="1" min="6" max="6" width="30.14"/>
-    <col customWidth="1" min="7" max="26" width="10.71"/>
+    <col customWidth="1" min="4" max="4" width="8.86"/>
+    <col customWidth="1" min="5" max="26" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -584,26 +585,26 @@
       <c r="L2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="4">
-        <v>5.0</v>
+      <c r="M2" s="5">
+        <v>3.0</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O2" s="4">
-        <v>4.0</v>
+      <c r="O2" s="5">
+        <v>3.0</v>
       </c>
       <c r="P2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="4">
-        <v>4.0</v>
+      <c r="Q2" s="5">
+        <v>2.0</v>
       </c>
       <c r="R2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="4">
-        <v>5.0</v>
+      <c r="S2" s="5">
+        <v>4.0</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>37</v>
